--- a/AAII_Financials/Quarterly/PH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PH_QTR_FIN.xlsx
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5755000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5486000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5174000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5084000</v>
       </c>
-      <c r="G8" s="3">
-        <v>5243100</v>
-      </c>
       <c r="H8" s="3">
+        <v>5243000</v>
+      </c>
+      <c r="I8" s="3">
         <v>4960000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4743000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4904000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5187200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5074400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4820900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4847500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5095900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5061700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4674800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4232800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4187800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4086400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3824600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3762800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3958900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>3746300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3411900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3230500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>3160600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>3702400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>3498000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>3334500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3681500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3687500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3472000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3479300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3817500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3749600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3370700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3364700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3496200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>3119100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2670800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>2743100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3573000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3452000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3234000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3168000</v>
       </c>
-      <c r="G9" s="3">
-        <v>3275100</v>
-      </c>
       <c r="H9" s="3">
+        <v>3275000</v>
+      </c>
+      <c r="I9" s="3">
         <v>3126000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3010000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3093000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3310000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3275700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3093000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3089300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3141900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3331800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3233600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2793000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2766200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2708200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2566600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2712900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2826700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>2709700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>2504000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2374300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2325500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2756500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2675100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2476400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2735800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2763900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2598700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2590400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2823200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2815500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2555400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2523800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2643700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2373400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2037900</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>2098000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2182000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2034000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1940000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1916000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1968000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1834000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1733000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1811000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1877200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1798700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1728000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1758100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1954100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1729900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1441200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1439800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1421600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1378200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1258000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1049900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1132200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1036600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>907900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>856200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>835100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>945900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>822900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>858100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>945700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>923600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>873300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>888900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>994300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>934100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>815300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>840900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>852500</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>745700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>632900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>645100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,13 +1248,14 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>310000</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>8</v>
@@ -1249,11 +1263,11 @@
       <c r="F12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H12" s="3">
         <v>298000</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1261,11 +1275,11 @@
       <c r="J12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="3">
+      <c r="K12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="3">
         <v>298000</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1273,11 +1287,11 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3">
         <v>331000</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>8</v>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,175 +1496,181 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E14" s="3">
         <v>31000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5000</v>
       </c>
-      <c r="F14" s="3">
-        <v>-56000</v>
-      </c>
       <c r="G14" s="3">
-        <v>27600</v>
+        <v>2000</v>
       </c>
       <c r="H14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I14" s="3">
         <v>20000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-220000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-31000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>67100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>24600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>15300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-31000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>259100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>52000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>37800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-252100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>17700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>25100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>23500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>55000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>7800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>5600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>18800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>15700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>47600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>13500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>9800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>7300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>7600</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>8600</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>33500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>17500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>45400</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>14000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>21400</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>16300</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>7900</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>10700</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E15" s="3">
         <v>235000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>233000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>232000</v>
       </c>
-      <c r="G15" s="3">
-        <v>229300</v>
-      </c>
       <c r="H15" s="3">
+        <v>230000</v>
+      </c>
+      <c r="I15" s="3">
         <v>222000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>226000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>229000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>230500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>228300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>227800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>240400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>209100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>225300</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4405000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4305000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4050000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4012000</v>
       </c>
-      <c r="G17" s="3">
-        <v>4070700</v>
-      </c>
       <c r="H17" s="3">
+        <v>4115000</v>
+      </c>
+      <c r="I17" s="3">
         <v>3887000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3763000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3920000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4057600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4058100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3868800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3933600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3824500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4148100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4048800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3254300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3419800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3358000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3153500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3160700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3245100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3099600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2875400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2756900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2715900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>3248300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>3243200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2901400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3168100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3158300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3040900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3019600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3319600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3279800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3010500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2990300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>3095600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>2804100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>2350100</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>2450900</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1181000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1124000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1072000</v>
       </c>
-      <c r="G18" s="3">
-        <v>1172300</v>
-      </c>
       <c r="H18" s="3">
+        <v>1128000</v>
+      </c>
+      <c r="I18" s="3">
         <v>1073000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>980000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>984000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1129700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1016200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>952200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>913900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1271400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>913600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>626000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>978500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>768000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>728400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>671100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>602100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>713800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>646700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>536500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>473600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>444700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>454100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>254800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>433100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>513400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>529200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>431100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>459700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>498000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>469800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>360200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>374400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>400600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>315000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>320700</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>292200</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,86 +2085,87 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-39000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-66000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-49000</v>
       </c>
-      <c r="F20" s="3">
-        <v>-8000</v>
-      </c>
       <c r="G20" s="3">
-        <v>-23200</v>
+        <v>-66000</v>
       </c>
       <c r="H20" s="3">
+        <v>-46000</v>
+      </c>
+      <c r="I20" s="3">
         <v>-34000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-65000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>30000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-35900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-49300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-58400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-6300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-41100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-39800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>37700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-357400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-578500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-231200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-119500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>29000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>13500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>104400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
@@ -2174,208 +2208,214 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1626000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1482000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1406000</v>
       </c>
-      <c r="F21" s="3">
-        <v>1312000</v>
-      </c>
       <c r="G21" s="3">
-        <v>1424900</v>
+        <v>1370000</v>
       </c>
       <c r="H21" s="3">
+        <v>1404000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1329000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1271000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1183000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1396100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1293800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1238300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1160600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1521500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1178700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>893400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>775100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>328900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>640000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>695800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>776600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>864600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>810700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>790700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>627600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>585900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>591800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>399000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>542200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>618700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>637500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>541200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>572200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>612700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>586900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>478300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>490400</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>519300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>402500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>394500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>367600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E22" s="3">
         <v>99000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>106000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>101000</v>
       </c>
-      <c r="G22" s="3">
-        <v>99200</v>
-      </c>
       <c r="H22" s="3">
+        <v>99000</v>
+      </c>
+      <c r="I22" s="3">
         <v>96000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>101000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>113000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>118800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>123700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>129000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>134500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>157200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>152000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>146900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>117800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>71300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>63300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>61400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>59400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>60300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>60800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>63000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>66000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>74500</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1340000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1119000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1064000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1040000</v>
       </c>
-      <c r="G23" s="3">
-        <v>1071100</v>
-      </c>
       <c r="H23" s="3">
+        <v>1071000</v>
+      </c>
+      <c r="I23" s="3">
         <v>995000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1166000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>875000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>986400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>920000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>868200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>820400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>903200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>756400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>516700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>503300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>118200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>434000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>490300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>571700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>657800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>599300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>577900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>413200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>364800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>454200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>254700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>433200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>513300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>529200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>431200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>459700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>497900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>469800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>360200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>374300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>400600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>315100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>320700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>292200</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>248000</v>
+      </c>
+      <c r="E24" s="3">
         <v>215000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>219000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>232000</v>
       </c>
-      <c r="G24" s="3">
-        <v>147500</v>
-      </c>
       <c r="H24" s="3">
+        <v>148000</v>
+      </c>
+      <c r="I24" s="3">
         <v>33000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>217000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>177000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>201200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>193300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>186100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>169400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>194100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>165400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>121300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>115300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-10700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>85900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>102600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>120300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>151900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>126100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>129400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>93100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>73500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>86800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>50100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>94100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>99600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>117800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>104800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>83800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>116600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>103700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-45100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>88800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>107300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>76200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>79300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>82000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1092000</v>
+      </c>
+      <c r="E26" s="3">
         <v>904000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>845000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>808000</v>
       </c>
-      <c r="G26" s="3">
-        <v>923600</v>
-      </c>
       <c r="H26" s="3">
+        <v>923000</v>
+      </c>
+      <c r="I26" s="3">
         <v>962000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>949000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>698000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>785100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>726700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>682100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>651100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>709100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>591000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>395500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>388000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>128900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>348100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>387700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>451500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>505900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>473200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>448500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>320100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>291300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>367400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>204600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>339000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>413700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>411400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>326400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>375900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>381300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>366100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>405300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>285500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>293400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>238800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>241400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>210200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1091000</v>
+      </c>
+      <c r="E27" s="3">
         <v>904000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>845000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>808000</v>
       </c>
-      <c r="G27" s="3">
-        <v>923200</v>
-      </c>
       <c r="H27" s="3">
+        <v>923000</v>
+      </c>
+      <c r="I27" s="3">
         <v>961000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>949000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>698000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>784700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>726600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>681900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>650800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>709000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>590900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>395200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>387900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>128800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>348000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>387600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>451200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>505700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>473200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>448400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>319800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>291300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>367300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>204500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>338900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>413700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>411200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>326200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>375700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>381300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>366000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>405200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>285400</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>293300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>238700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>241300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3224,8 +3285,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3236,29 +3297,29 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-14500</v>
       </c>
-      <c r="AH29" s="3" t="s">
+      <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-28000</v>
       </c>
-      <c r="AJ29" s="3">
-        <v>0</v>
-      </c>
       <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-349000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,86 +3583,89 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E32" s="3">
         <v>66000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>49000</v>
       </c>
-      <c r="F32" s="3">
-        <v>8000</v>
-      </c>
       <c r="G32" s="3">
-        <v>23200</v>
+        <v>66000</v>
       </c>
       <c r="H32" s="3">
+        <v>46000</v>
+      </c>
+      <c r="I32" s="3">
         <v>34000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>65000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-30000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>35900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>49300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>58400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>6300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>41100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>39800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-37700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>357400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>578500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>231200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>119500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-29000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-13500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-104400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5400</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
@@ -3638,130 +3708,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1091000</v>
+      </c>
+      <c r="E33" s="3">
         <v>904000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>845000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>808000</v>
       </c>
-      <c r="G33" s="3">
-        <v>923200</v>
-      </c>
       <c r="H33" s="3">
+        <v>923000</v>
+      </c>
+      <c r="I33" s="3">
         <v>961000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>949000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>698000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>784700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>726600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>681900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>650800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>709000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>590900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>395200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>387900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>128800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>348000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>387600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>451200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>505700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>473200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>448400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>319800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>291300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>367300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>204500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>338900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>413700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>411200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>311700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>375700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>353300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>366000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>56200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>285400</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>293300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>238700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>241300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1091000</v>
+      </c>
+      <c r="E35" s="3">
         <v>904000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>845000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>808000</v>
       </c>
-      <c r="G35" s="3">
-        <v>923200</v>
-      </c>
       <c r="H35" s="3">
+        <v>923000</v>
+      </c>
+      <c r="I35" s="3">
         <v>961000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>949000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>698000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>784700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>726600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>681900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>650800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>709000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>590900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>395200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>387900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>128800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>348000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>387600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>451200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>505700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>473200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>448400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>319800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>291300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>367300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>204500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>338900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>413700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>411200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>311700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>375700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>353300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>366000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>56200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>285400</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>293300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>238700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>241300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>501000</v>
+      </c>
+      <c r="E41" s="3">
         <v>476000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>427000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>473000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>467000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>408700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>395500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>371100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>422000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>405500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>382800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>448900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>475200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>534800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>756100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>502300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>535800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>467700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>449500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>478600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>733100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>489600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>564700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>742400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>685500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>697600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>948400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3627400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3219800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1098700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1047400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>952100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>822100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1089500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1024800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>874800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>884900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>819600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1520700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1393900</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4371,376 +4461,385 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>10000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>11100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7900</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>23500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>21600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>19500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>27900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>38600</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>40500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>40200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>39100</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>40300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>43300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>33500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>70800</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>92500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>145100</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>282100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>150900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>70200</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>31000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>40800</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>33000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>101200</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>108000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>99800</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>39300</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>36800</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>684300</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>746700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3669000</v>
+      </c>
+      <c r="E43" s="3">
         <v>3659000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3241000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3372000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3377000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3291900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2888600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3180100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3334000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3349700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3053800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3146600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3260200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3329000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3065200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3118500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2913800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2709600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2377500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2451200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2544100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2463600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2161700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2165500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2130100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2524400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2319300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2297400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2441800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2434500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2263000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2377300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2473900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2474500</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2170500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2188700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2185700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2105200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1667600</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1748900</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3166000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3179000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3152000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3081000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2839000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2822500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2807000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2872300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2787000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2966300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3092900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3028700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2907900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3067600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3095700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3130200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2214600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2330200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2307300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2264700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2090600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1898200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1870900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1795800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1964200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2011400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2014300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1790000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1678100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1756000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1804600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1762600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1621300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1732800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1780300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1707000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1549500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1538600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1241600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1248000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>361100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6300</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>8</v>
@@ -4748,216 +4847,222 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>18900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>346400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>397300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6354600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2683600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2732900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>396700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>209800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>157400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>159000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>132400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>184200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>155500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>234100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>141100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>182500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>178400</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>188900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>165200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>134900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>165100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>202800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>134400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>120300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>119000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>133600</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>144400</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7695000</v>
+      </c>
+      <c r="E46" s="3">
         <v>7608000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7193000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>7227000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6950000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6777100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6348500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7033700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6799000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6942600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6729900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6829600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6834200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7233400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7285000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7167800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12046600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>8229700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>7907600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5631300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5616800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5049100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4799700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4869500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5034800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5481400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5661200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8138100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7673100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>5537800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>5334700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>5298100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>5085200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>5563100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>5286400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>5004600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>4779700</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>4619200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5247800</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>5281900</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>282000</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>8</v>
@@ -4965,83 +5070,83 @@
       <c r="F47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3">
         <v>280000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1180800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1202900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1236800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>294000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1124800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1130900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1084000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>826600</v>
       </c>
-      <c r="P47" s="3" t="s">
+      <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>26800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>27100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>314800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>2500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>294100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>2100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>2100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>319500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>1500</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>1100</v>
       </c>
       <c r="AD47" s="3">
         <v>1100</v>
       </c>
       <c r="AE47" s="3">
+        <v>1100</v>
+      </c>
+      <c r="AF47" s="3">
         <v>316700</v>
-      </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>8</v>
@@ -5052,273 +5157,282 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ47" s="3">
-        <v>0</v>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK47" s="3">
         <v>0</v>
       </c>
       <c r="AL47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="3">
         <v>3900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>15100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>30800</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>32800</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>18500</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3221000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2959000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2966000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2972000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3129000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2821600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2801000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2839500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3102000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2870900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2905700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2840500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3097800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2843800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2839500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2753600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2256200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2174200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2202900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2223500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2398400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2249100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>2302100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2292900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2431300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2434700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2491800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2016900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1768300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1779900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1793800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1828000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1856200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1941800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1937100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1962800</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1937300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1945700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1506200</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1562900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>18389000</v>
+      </c>
+      <c r="E49" s="3">
         <v>18521000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>18759000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>18901000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>18068000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>17832500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>17802000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>18372500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>18323000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>18541300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>18825400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>18715100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>19079200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>19118100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>19056800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>18772100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>10875900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>11208900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>11343500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11435900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>11579500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>11626800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>11796200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>11715200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>11668800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>11711600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>11991300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8512400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>7237100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>7294400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>7346400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>7441200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>7519900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>7881000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>7872800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>7894500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>7894400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>7847100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>3662900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>3812700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1037000</v>
+      </c>
+      <c r="E52" s="3">
         <v>1307000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1303000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1290000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>781000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>20000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>666000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>21600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1162900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1312700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1234200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>450400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>931900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>939400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>943700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>452500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>914500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>927500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>906200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>433300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>736100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>898600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>900100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>581500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>865900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>832800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>857700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>858700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>851600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>868900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>865400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>863400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>882600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1281800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1294900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>30877000</v>
+      </c>
+      <c r="E54" s="3">
         <v>30679000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>30511000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30677000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29494000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28917800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28271500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29600800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29298000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29578300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29694900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29592700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29964500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>30515700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>30520900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29954900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25943900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>22545300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>22395500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>20236900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>20341200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>19841500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>19827400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>19785900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19887800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20365300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21044000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19568600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>17576700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>15477900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>15307700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>15425000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>15320100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>16237500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>15965200</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>15731300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>15489900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>15325300</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>11731600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>11970900</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2439000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2296000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2054000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2150000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2126000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1981000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1794900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1953500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1992000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1964200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1971900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2036800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2050900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2080100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1966800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2018200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1731900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1732400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1597000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1636300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1667900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1551500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1343000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1265000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1111800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1422000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1311700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1287400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1413200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1423700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1307200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1404700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1430300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1376500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1229300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1304300</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1300500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>1209400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>997200</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>1017900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1803000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2813000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2386000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2848000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1838000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1951500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2373300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3515600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3457000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4080800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3681200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3594400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3813700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1992900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1994300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1725100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1724300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1923900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2201700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>302300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>186400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>610900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>884500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>809500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1035200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1604300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1736800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>587000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1017300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1144300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>796900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>638500</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1055500</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1248200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1144100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1008500</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>776200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>581500</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>596000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1196000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1283000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1158000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1349000</v>
       </c>
-      <c r="G59" s="3">
-        <v>631000</v>
-      </c>
       <c r="H59" s="3">
+        <v>1268000</v>
+      </c>
+      <c r="I59" s="3">
         <v>570000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>554000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>643200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>539000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>569900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>530600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>727800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>619400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>520100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1742300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1755400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2403100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1750400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1458800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1344700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1425800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1298800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1253200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1178800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1227100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1216400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1175100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1133100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1151600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1108000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1057400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1106900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1128700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1076500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1060200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1018800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1086900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1062900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>846800</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>880400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6096000</v>
+      </c>
+      <c r="E60" s="3">
         <v>6737000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6086000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6779000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5819000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5614500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5987300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7338000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7313000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7994400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7497100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7667100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7735400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5788200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5703400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5498700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5859300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5406700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>5257500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3283200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3096500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3036600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3207100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3328200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3148400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3673600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4091100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4157300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3151800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3549000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3508900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3308500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3197500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>3508500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3537700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3467100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>3395900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>3048400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2425500</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>2494200</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6930000</v>
+      </c>
+      <c r="E61" s="3">
         <v>6769000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7484000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7485000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7648000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>7421400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6668000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6673300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7337000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7290200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8108700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8596100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8983700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11412300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12025900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>12238900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9755800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>6229700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>6250500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>6263900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>6582100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>6571900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6602300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7057700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7652300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>8097900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8141200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7366900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6520800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4284200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4303300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4313200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4318600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4818600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4798400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>4788100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>4861900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>5255200</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>2653600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2653000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>489000</v>
+      </c>
+      <c r="E62" s="3">
         <v>625000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>666000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>686000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>508000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>594700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>602500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>626300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>468000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>637200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>636300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>617700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>627700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>855200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3457100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3443900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1468900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1936100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2119200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2183800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2249000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2825100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>2895700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>2855700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>2845400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>2286300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>2469100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1941600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1935900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1628700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1674300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1696200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1938600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>2034100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>2109900</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>1945300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>1964800</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>2274000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>2121600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>2173100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15464000</v>
+      </c>
+      <c r="E66" s="3">
         <v>16062000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16191000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16891000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>15803000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15518000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15144400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16699500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>17217000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>17977900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18382600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>19017800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19626200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>20722600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>21198500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>21192400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17095900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13585500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13640400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11746100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11942900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>12449300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12721400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>13257000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>13660500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>14069300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14713800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>13472000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>11614700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9468000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9492500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9323700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9460200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>10367100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>10451800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>10206300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>10228300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>10583200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>7203900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7323600</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>24487000</v>
+      </c>
+      <c r="E72" s="3">
         <v>23649000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>22972000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22355000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>21775000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>21082300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>20331500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>19593100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19105000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>18529600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>17993500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>17501900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>17041500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>16522900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>16102900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15878600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15661800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15704200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15488800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15233800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14915500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>14429900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14072200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13738500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13643900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13348300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13094300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13003100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12777500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12427200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12114400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>11902300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>11626000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>11373700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>11095700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>11127600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>10930300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>10725300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>10579600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>10427200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15404000</v>
+      </c>
+      <c r="E76" s="3">
         <v>14609000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>14311000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>13777000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>13682000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13391000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13118600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>12891900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12072000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11590900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11302600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>10565400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>10326900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9781300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9322400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8762500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8848000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8959900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8755100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8490800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8398300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7392200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7106000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6529000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>6227200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6296000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6330200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6096600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5962000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6010000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5815200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6101400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5859900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5870400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5513400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5524900</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5261600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4742100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4527700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4647300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1091000</v>
+      </c>
+      <c r="E81" s="3">
         <v>904000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>845000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>808000</v>
       </c>
-      <c r="G81" s="3">
-        <v>923200</v>
-      </c>
       <c r="H81" s="3">
+        <v>923000</v>
+      </c>
+      <c r="I81" s="3">
         <v>961000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>949000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>698000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>784700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>726600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>681900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>650800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>709000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>590900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>395200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>387900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>128800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>348000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>387600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>451200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>505700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>473200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>448400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>319800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>291300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>367300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>204500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>338900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>413700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>411200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>311700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>375700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>353300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>366000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>56200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>285400</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>293300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>238700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>241300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E83" s="3">
         <v>86000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>88000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>89000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>91300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>87100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>85800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>84900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>82800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>80200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>87500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>67000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>62400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>63800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>229700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>154000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>139400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>142700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>144100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>145500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>146600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>150500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>149800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>148400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>146600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>137600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>144200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>109100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>105400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>108300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>110100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>112500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>114800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>117100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>118100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>116100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>118700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>87500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>73800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>75300</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1736000</v>
+      </c>
+      <c r="E89" s="3">
         <v>984000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>862000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>782000</v>
       </c>
-      <c r="G89" s="3">
-        <v>1467200</v>
-      </c>
       <c r="H89" s="3">
+        <v>1467000</v>
+      </c>
+      <c r="I89" s="3">
         <v>630000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>935000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>744000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1236900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>795100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>702000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>650000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1185000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>718800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>618800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>457400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>893300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>543000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>581100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>424400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>693600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>527400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>616600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>737400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>780100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>464900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>376800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>449100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>637500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>551600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>381700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>159400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>695500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>444500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>221400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>239000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>513200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>385100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>290200</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>113900</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-173000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-103000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-94000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-89000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-130800</v>
-      </c>
       <c r="H91" s="3">
+        <v>-131000</v>
+      </c>
+      <c r="I91" s="3">
         <v>-88000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-121000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-95000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-116700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-79200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-106400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-97700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-108100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-86900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-102100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-83600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-71200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-53300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-57400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-48200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-73900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-43200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-50800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-50100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-63900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-68200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-50300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-50000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-50600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-52300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-42100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-53400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-49500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-65400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-79300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-58500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-73900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-38800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-32500</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-93000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-68000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1078000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-120700</v>
-      </c>
       <c r="H94" s="3">
+        <v>-121000</v>
+      </c>
+      <c r="I94" s="3">
         <v>-67000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>499000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-87000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-103700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-63200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-75100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-56000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-91900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-63200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-94300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-7927400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-293100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-51400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-32400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-41900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-51400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-27300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>74800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>3900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>21200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>109900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3302100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1853000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-102400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-84800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-16200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-15100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>203100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-41200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-24500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-117300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-56800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-3410700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>57100</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>45200</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,25 +10455,26 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E96" s="3">
         <v>227000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>228000</v>
       </c>
       <c r="F96" s="3">
         <v>228000</v>
       </c>
       <c r="G96" s="3">
-        <v>230800</v>
+        <v>228000</v>
       </c>
       <c r="H96" s="3">
-        <v>210000</v>
+        <v>231000</v>
       </c>
       <c r="I96" s="3">
         <v>210000</v>
@@ -10249,82 +10483,82 @@
         <v>210000</v>
       </c>
       <c r="K96" s="3">
+        <v>210000</v>
+      </c>
+      <c r="L96" s="3">
         <v>209800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>190500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>190300</v>
-      </c>
-      <c r="N96" s="3">
-        <v>190400</v>
       </c>
       <c r="O96" s="3">
         <v>190400</v>
       </c>
       <c r="P96" s="3">
+        <v>190400</v>
+      </c>
+      <c r="Q96" s="3">
         <v>170500</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-171200</v>
       </c>
       <c r="R96" s="3">
         <v>-171200</v>
       </c>
       <c r="S96" s="3">
+        <v>-171200</v>
+      </c>
+      <c r="T96" s="3">
         <v>-171800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-132500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-132600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-132900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-133800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-114100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-113700</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-113500</v>
       </c>
       <c r="AA96" s="3">
         <v>-113500</v>
       </c>
       <c r="AB96" s="3">
+        <v>-113500</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-113300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-113700</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-113400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-113500</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-98500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-99600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-100900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-101000</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-88100</v>
       </c>
       <c r="AK96" s="3">
         <v>-88100</v>
@@ -10333,19 +10567,22 @@
         <v>-88100</v>
       </c>
       <c r="AM96" s="3">
-        <v>-88200</v>
+        <v>-88100</v>
       </c>
       <c r="AN96" s="3">
         <v>-88200</v>
       </c>
       <c r="AO96" s="3">
+        <v>-88200</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-84200</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-84700</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1564000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-841000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-835000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>306000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1296000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-577000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1393000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-711000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1109500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-700300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-687400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-617900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1155800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-880200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-274600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1339600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3116400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-466400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1686600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-421000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-407700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-606400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-916500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-692700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-823400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-781600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>215900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1838400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1592500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-430200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-252700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-7200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1146400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-352700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-47400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-135400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-385700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>2309000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-156100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>15500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E101" s="3">
         <v>27000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-16000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-7100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-15100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-23900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-6900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-15100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-23900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>9000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>31100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>47500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>8300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>10000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-44000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>30300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-26900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-6600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>14800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-17400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-7100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-19500</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>10600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>4600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-5300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>15300</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-64300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-2400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E102" s="3">
         <v>49000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-46000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6000</v>
       </c>
-      <c r="G102" s="3">
-        <v>58300</v>
-      </c>
       <c r="H102" s="3">
+        <v>58000</v>
+      </c>
+      <c r="I102" s="3">
         <v>13000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>25000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-51000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>22700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-66100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-59600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-221200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>253700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6145600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3692700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2243300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-39500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>243500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-75100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-177700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>56900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-250700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2679000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>407600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>2121000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>51300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>95300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>130000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-267400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>64800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>150000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>65300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-701200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>126900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>172200</v>
       </c>
     </row>
